--- a/backreand/test.xlsx
+++ b/backreand/test.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\41414\Desktop\code\exlcode\backreand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D280996-255B-473C-83B7-32A03306EA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7867DC07-EAF9-4A60-9A6E-5FB420E34DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E8188A2-568D-412F-AC58-6957F833817A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E8188A2-568D-412F-AC58-6957F833817A}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="1" r:id="rId1"/>
+    <sheet name="tes2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>土豆</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,6 +49,18 @@
   </si>
   <si>
     <t>冰箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花籃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -444,4 +457,40 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C667F328-4F6B-4C7A-A001-296D2D911CB6}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/backreand/test.xlsx
+++ b/backreand/test.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\41414\Desktop\code\exlcode\backreand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7867DC07-EAF9-4A60-9A6E-5FB420E34DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B253BF-EFE9-44CF-A3E2-F8344E5A08BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E8188A2-568D-412F-AC58-6957F833817A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E8188A2-568D-412F-AC58-6957F833817A}"/>
   </bookViews>
   <sheets>
-    <sheet name="test" sheetId="1" r:id="rId1"/>
-    <sheet name="tes2" sheetId="2" r:id="rId2"/>
+    <sheet name="申請資料" sheetId="1" r:id="rId1"/>
+    <sheet name="車位資料" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,37 +38,403 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>土豆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>花籃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>台中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="130">
+  <si>
+    <t>員編</t>
+  </si>
+  <si>
+    <t>姓名</t>
+  </si>
+  <si>
+    <t>單位</t>
+  </si>
+  <si>
+    <t>是否申請</t>
+  </si>
+  <si>
+    <t>備註</t>
+  </si>
+  <si>
+    <t>E001</t>
+  </si>
+  <si>
+    <t>測試人員001</t>
+  </si>
+  <si>
+    <t>資訊課</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>延續申請</t>
+  </si>
+  <si>
+    <t>E002</t>
+  </si>
+  <si>
+    <t>測試人員002</t>
+  </si>
+  <si>
+    <t>總務課</t>
+  </si>
+  <si>
+    <t>E003</t>
+  </si>
+  <si>
+    <t>測試人員003</t>
+  </si>
+  <si>
+    <t>會計課</t>
+  </si>
+  <si>
+    <t>E004</t>
+  </si>
+  <si>
+    <t>測試人員004</t>
+  </si>
+  <si>
+    <t>人事課</t>
+  </si>
+  <si>
+    <t>E005</t>
+  </si>
+  <si>
+    <t>測試人員005</t>
+  </si>
+  <si>
+    <t>行政課</t>
+  </si>
+  <si>
+    <t>E006</t>
+  </si>
+  <si>
+    <t>測試人員006</t>
+  </si>
+  <si>
+    <t>業務課</t>
+  </si>
+  <si>
+    <t>E007</t>
+  </si>
+  <si>
+    <t>測試人員007</t>
+  </si>
+  <si>
+    <t>E008</t>
+  </si>
+  <si>
+    <t>測試人員008</t>
+  </si>
+  <si>
+    <t>E009</t>
+  </si>
+  <si>
+    <t>測試人員009</t>
+  </si>
+  <si>
+    <t>E010</t>
+  </si>
+  <si>
+    <t>測試人員010</t>
+  </si>
+  <si>
+    <t>E011</t>
+  </si>
+  <si>
+    <t>測試人員011</t>
+  </si>
+  <si>
+    <t>E012</t>
+  </si>
+  <si>
+    <t>測試人員012</t>
+  </si>
+  <si>
+    <t>E013</t>
+  </si>
+  <si>
+    <t>測試人員013</t>
+  </si>
+  <si>
+    <t>E014</t>
+  </si>
+  <si>
+    <t>測試人員014</t>
+  </si>
+  <si>
+    <t>E015</t>
+  </si>
+  <si>
+    <t>測試人員015</t>
+  </si>
+  <si>
+    <t>E016</t>
+  </si>
+  <si>
+    <t>測試人員016</t>
+  </si>
+  <si>
+    <t>E017</t>
+  </si>
+  <si>
+    <t>測試人員017</t>
+  </si>
+  <si>
+    <t>E018</t>
+  </si>
+  <si>
+    <t>測試人員018</t>
+  </si>
+  <si>
+    <t>E019</t>
+  </si>
+  <si>
+    <t>測試人員019</t>
+  </si>
+  <si>
+    <t>E020</t>
+  </si>
+  <si>
+    <t>測試人員020</t>
+  </si>
+  <si>
+    <t>E021</t>
+  </si>
+  <si>
+    <t>測試人員021</t>
+  </si>
+  <si>
+    <t>E022</t>
+  </si>
+  <si>
+    <t>測試人員022</t>
+  </si>
+  <si>
+    <t>E023</t>
+  </si>
+  <si>
+    <t>測試人員023</t>
+  </si>
+  <si>
+    <t>E024</t>
+  </si>
+  <si>
+    <t>測試人員024</t>
+  </si>
+  <si>
+    <t>E025</t>
+  </si>
+  <si>
+    <t>測試人員025</t>
+  </si>
+  <si>
+    <t>E026</t>
+  </si>
+  <si>
+    <t>測試人員026</t>
+  </si>
+  <si>
+    <t>E027</t>
+  </si>
+  <si>
+    <t>測試人員027</t>
+  </si>
+  <si>
+    <t>E028</t>
+  </si>
+  <si>
+    <t>測試人員028</t>
+  </si>
+  <si>
+    <t>E029</t>
+  </si>
+  <si>
+    <t>測試人員029</t>
+  </si>
+  <si>
+    <t>E030</t>
+  </si>
+  <si>
+    <t>測試人員030</t>
+  </si>
+  <si>
+    <t>E031</t>
+  </si>
+  <si>
+    <t>測試人員031</t>
+  </si>
+  <si>
+    <t>E032</t>
+  </si>
+  <si>
+    <t>測試人員032</t>
+  </si>
+  <si>
+    <t>E033</t>
+  </si>
+  <si>
+    <t>測試人員033</t>
+  </si>
+  <si>
+    <t>E034</t>
+  </si>
+  <si>
+    <t>測試人員034</t>
+  </si>
+  <si>
+    <t>E035</t>
+  </si>
+  <si>
+    <t>測試人員035</t>
+  </si>
+  <si>
+    <t>E036</t>
+  </si>
+  <si>
+    <t>測試人員036</t>
+  </si>
+  <si>
+    <t>E037</t>
+  </si>
+  <si>
+    <t>測試人員037</t>
+  </si>
+  <si>
+    <t>E038</t>
+  </si>
+  <si>
+    <t>測試人員038</t>
+  </si>
+  <si>
+    <t>E039</t>
+  </si>
+  <si>
+    <t>測試人員039</t>
+  </si>
+  <si>
+    <t>E040</t>
+  </si>
+  <si>
+    <t>測試人員040</t>
+  </si>
+  <si>
+    <t>E041</t>
+  </si>
+  <si>
+    <t>測試人員041</t>
+  </si>
+  <si>
+    <t>E042</t>
+  </si>
+  <si>
+    <t>測試人員042</t>
+  </si>
+  <si>
+    <t>E043</t>
+  </si>
+  <si>
+    <t>測試人員043</t>
+  </si>
+  <si>
+    <t>E044</t>
+  </si>
+  <si>
+    <t>測試人員044</t>
+  </si>
+  <si>
+    <t>E045</t>
+  </si>
+  <si>
+    <t>測試人員045</t>
+  </si>
+  <si>
+    <t>E046</t>
+  </si>
+  <si>
+    <t>測試人員046</t>
+  </si>
+  <si>
+    <t>E047</t>
+  </si>
+  <si>
+    <t>測試人員047</t>
+  </si>
+  <si>
+    <t>E048</t>
+  </si>
+  <si>
+    <t>測試人員048</t>
+  </si>
+  <si>
+    <t>E049</t>
+  </si>
+  <si>
+    <t>測試人員049</t>
+  </si>
+  <si>
+    <t>E050</t>
+  </si>
+  <si>
+    <t>測試人員050</t>
+  </si>
+  <si>
+    <t>E051</t>
+  </si>
+  <si>
+    <t>測試人員051</t>
+  </si>
+  <si>
+    <t>E052</t>
+  </si>
+  <si>
+    <t>測試人員052</t>
+  </si>
+  <si>
+    <t>E053</t>
+  </si>
+  <si>
+    <t>測試人員053</t>
+  </si>
+  <si>
+    <t>E054</t>
+  </si>
+  <si>
+    <t>測試人員054</t>
+  </si>
+  <si>
+    <t>E055</t>
+  </si>
+  <si>
+    <t>測試人員055</t>
+  </si>
+  <si>
+    <t>E056</t>
+  </si>
+  <si>
+    <t>測試人員056</t>
+  </si>
+  <si>
+    <t>E057</t>
+  </si>
+  <si>
+    <t>測試人員057</t>
+  </si>
+  <si>
+    <t>E999</t>
+  </si>
+  <si>
+    <t>新增申請者</t>
+  </si>
+  <si>
+    <t>本期新增，應放最後</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -83,6 +449,19 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -107,10 +486,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -425,31 +806,1010 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D17C0C9F-D2A9-4B68-A541-744E42713937}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E59"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>30</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -461,34 +1821,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C667F328-4F6B-4C7A-A001-296D2D911CB6}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
